--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23C.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_D942D06410F3F73A3B40CD60608D569FD9DE9628" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{8060FC76-30F4-4E3E-8A43-5ECF0D155B2D}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -12,20 +18,22 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
-    <sheet name="Tabla_468859" sheetId="6" r:id="rId6"/>
+    <sheet name="Hidden_5" sheetId="6" r:id="rId6"/>
+    <sheet name="Tabla_468859" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_15">Hidden_1!$A$1:$A$3</definedName>
     <definedName name="Hidden_26">Hidden_2!$A$1:$A$10</definedName>
     <definedName name="Hidden_311">Hidden_3!$A$1:$A$4</definedName>
     <definedName name="Hidden_413">Hidden_4!$A$1:$A$3</definedName>
+    <definedName name="Hidden_514">Hidden_5!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="120">
   <si>
     <t>50878</t>
   </si>
@@ -105,6 +113,9 @@
     <t>468854</t>
   </si>
   <si>
+    <t>571963</t>
+  </si>
+  <si>
     <t>468855</t>
   </si>
   <si>
@@ -180,7 +191,7 @@
     <t>Descripción de unidad, por ejemplo: spot de 30 segundos (radio); mensaje en TV 20 segundos</t>
   </si>
   <si>
-    <t>Concepto o campaña</t>
+    <t>Concepto o campaña (Redactada con perspectiva de género)</t>
   </si>
   <si>
     <t>Clave única de identificación de campaña o aviso institucional, en su caso</t>
@@ -195,7 +206,10 @@
     <t>Ámbito geográfico de cobertura</t>
   </si>
   <si>
-    <t>Sexo (catálogo)</t>
+    <t>ESTE CRITERIO APLICA PARA EJERCICIOS ANTERIORES AL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
   </si>
   <si>
     <t xml:space="preserve">Lugar de residencia </t>
@@ -216,7 +230,7 @@
     <t>Distintivo y/o nombre comercial del concesionario responsable de publicar la campaña o comunicación</t>
   </si>
   <si>
-    <t>Descripción breve de las razones que justifican la elección del proveedor</t>
+    <t>Descripción breve de las razones que justifican la elección del/la proveedor/a (Redactada con perspectiva de género)</t>
   </si>
   <si>
     <t>Monto total del tiempo de Estado o tiempo fiscal consumidos</t>
@@ -250,49 +264,43 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>4EDF43B4EF404831325B6C7D8039EDEC</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
     <t>Preparatoria</t>
   </si>
   <si>
     <t>15 años en adelante</t>
   </si>
   <si>
-    <t>4709809</t>
-  </si>
-  <si>
     <t>Departamento de Información y Relaciones Públicas del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
-    <t>03/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no tiene inherencia en la utilización de Tiempos Oficiales por lo que hago mención de dos mensajes aclaratorios e informativos: Menasje 1:"La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales está a cargo de la Dirección General de Radio, Televisión y Cinematografía de la Secretaría de Gabernación." Mensaje 2:" La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales esta a cargo del Instituto Nacional Electoral." Por lo que no se genera información alguna.</t>
-  </si>
-  <si>
-    <t>4289428</t>
-  </si>
-  <si>
-    <t>3122340</t>
-  </si>
-  <si>
-    <t>2816098</t>
-  </si>
-  <si>
-    <t>2644462</t>
+    <t>CA9656B8DBE4CBCCB9A5A1DE4B813FCF</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>8540623</t>
+  </si>
+  <si>
+    <t>03/10/2023</t>
+  </si>
+  <si>
+    <t>09/01/2024</t>
+  </si>
+  <si>
+    <t>Durante el periodo 01 de octubre de 2023 al 31 de diciembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no tiene inherencia en la utilización de Tiempos Oficiales por lo que hago mención de dos mensajes aclaratorios e informativos: Menasje 1:"La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales está a cargo de la Dirección General de Radio, Televisión y Cinematografía de la Secretaría de Gabernación." Mensaje 2:" La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales esta a cargo del Instituto Nacional Electoral." Por lo que no se genera información alguna.</t>
   </si>
   <si>
     <t>Tiempo de estado</t>
@@ -355,6 +363,15 @@
     <t>Femenino y masculino</t>
   </si>
   <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujeres y Hombres</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
@@ -377,33 +394,12 @@
   </si>
   <si>
     <t xml:space="preserve">Presupuesto ejercido al periodo reportado de cada partida </t>
-  </si>
-  <si>
-    <t>40D5252ED2749727E0CD7FA45943FEDD</t>
-  </si>
-  <si>
-    <t>Ver nota</t>
-  </si>
-  <si>
-    <t>7708F73158F3CAE24A002A097DE33713</t>
-  </si>
-  <si>
-    <t>613CAFD2F38DE453954367206E5B792C</t>
-  </si>
-  <si>
-    <t>7526AFAFFBF6C22672C718A2EF3BC581</t>
-  </si>
-  <si>
-    <t>Ver Nota</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -502,6 +498,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -517,44 +516,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -582,14 +581,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -617,6 +633,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -628,175 +661,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -804,37 +813,37 @@
     <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="79.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="62.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="77.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="85" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="87.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="62" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="75.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="44.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="46.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="86" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="255" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="85" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="87.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="99.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="52" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="75.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="86" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -851,7 +860,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -866,7 +875,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -907,58 +916,61 @@
         <v>8</v>
       </c>
       <c r="O4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P4" t="s">
         <v>9</v>
       </c>
       <c r="Q4" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" t="s">
         <v>6</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>9</v>
-      </c>
-      <c r="S4" t="s">
-        <v>6</v>
       </c>
       <c r="T4" t="s">
         <v>6</v>
       </c>
       <c r="U4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V4" t="s">
         <v>9</v>
-      </c>
-      <c r="V4" t="s">
-        <v>6</v>
       </c>
       <c r="W4" t="s">
         <v>6</v>
       </c>
       <c r="X4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="s">
         <v>7</v>
       </c>
       <c r="Z4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="s">
         <v>10</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>6</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>9</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>7</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>11</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -1049,10 +1061,13 @@
       <c r="AE5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1084,197 +1099,204 @@
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
       <c r="AE6" s="5"/>
-    </row>
-    <row r="7" spans="1:31" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="AF6" s="5"/>
+    </row>
+    <row r="7" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>78</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="S8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="AD8" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AE6"/>
+    <mergeCell ref="A6:AF6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1282,18 +1304,21 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F195">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F198" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_15</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G195">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G198" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_26</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L195">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L198" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>Hidden_311</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N8:N195">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N8:N198" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>Hidden_413</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O8:O198" xr:uid="{00000000-0002-0000-0000-000004000000}">
+      <formula1>Hidden_514</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1301,7 +1326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1326,7 +1351,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1386,7 +1411,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1416,7 +1441,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1441,12 +1466,35 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="62.5703125" bestFit="1" customWidth="1"/>
@@ -1457,104 +1505,36 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
